--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,10 +491,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.293866395950317</v>
+        <v>1.356818199157715</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9871368975242844</v>
+        <v>0.9893529482385016</v>
       </c>
       <c r="F2" t="n">
         <v>0.987012987012987</v>
@@ -503,7 +503,7 @@
         <v>0.9824284292349985</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9980041603418226</v>
+        <v>0.9991285770506549</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.374776363372803</v>
+        <v>1.340761184692383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9911925468523709</v>
+        <v>0.9930738987942377</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9824284292349985</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9997470062405128</v>
+        <v>0.9997610614493732</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.293866395950317</v>
+        <v>1.356818199157715</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9871368975242844</v>
+        <v>0.9893529482385016</v>
       </c>
       <c r="F2" t="n">
         <v>0.987012987012987</v>
@@ -634,7 +634,7 @@
         <v>0.9824284292349985</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9980041603418226</v>
+        <v>0.9991285770506549</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.374776363372803</v>
+        <v>1.340761184692383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9911925468523709</v>
+        <v>0.9930738987942377</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9824284292349985</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9997470062405128</v>
+        <v>0.9997610614493732</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.356818199157715</v>
+        <v>0.7807161808013916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9893529482385016</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9991285770506549</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.340761184692383</v>
+        <v>0.9821460247039795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9930738987942377</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9997610614493732</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.356818199157715</v>
+        <v>0.7807161808013916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9893529482385016</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9991285770506549</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.340761184692383</v>
+        <v>0.9821460247039795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9930738987942377</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9824284292349985</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9997610614493732</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7807161808013916</v>
+        <v>1.208144664764404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.8362854771547502</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8707482993197279</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8090322881672265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9714355129807025</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,21 +526,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9821460247039795</v>
+        <v>1.315556526184082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8389450502746962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8707482993197279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8090322881672265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9714355129807025</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.246099948883057</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8304702033601868</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8707482993197279</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8090322881672265</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9740038872691934</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7807161808013916</v>
+        <v>1.208144664764404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.8362854771547502</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8707482993197279</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8090322881672265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9714355129807025</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,21 +692,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9821460247039795</v>
+        <v>1.315556526184082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8389450502746962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8707482993197279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8090322881672265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9714355129807025</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.246099948883057</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8304702033601868</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8707482993197279</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8090322881672265</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9740038872691934</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.208144664764404</v>
+        <v>44.7150092124939</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8362854771547502</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8090322881672265</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9714355129807025</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.315556526184082</v>
+        <v>61.17642974853516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8389450502746962</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8090322881672265</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9714355129807025</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,19 +561,19 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.246099948883057</v>
+        <v>137.197586774826</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8304702033601868</v>
+        <v>0.9202278598090171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8090322881672265</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9740038872691934</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.208144664764404</v>
+        <v>44.7150092124939</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8362854771547502</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8090322881672265</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9714355129807025</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -692,19 +692,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.315556526184082</v>
+        <v>61.17642974853516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8389450502746962</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8090322881672265</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9714355129807025</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.246099948883057</v>
+        <v>137.197586774826</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8304702033601868</v>
+        <v>0.9202278598090171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8090322881672265</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9740038872691934</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>44.7150092124939</v>
+        <v>1.012442588806152</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.939873417721519</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9169917656074629</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9807870872172846</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>61.17642974853516</v>
+        <v>1.440536022186279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9193219807675821</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9413118527042578</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9190787698855583</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9801950104776356</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>137.197586774826</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9202278598090171</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.939873417721519</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9169917656074629</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9807870872172846</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>44.7150092124939</v>
+        <v>1.012442588806152</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.939873417721519</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9169917656074629</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9807870872172846</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>61.17642974853516</v>
+        <v>1.440536022186279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9193219807675821</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9413118527042578</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9190787698855583</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9801950104776356</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>137.197586774826</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9202278598090171</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.939873417721519</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9169917656074629</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9807870872172846</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.012442588806152</v>
+        <v>1.048494338989258</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.440536022186279</v>
+        <v>1.40929388999939</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.012442588806152</v>
+        <v>1.048494338989258</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.440536022186279</v>
+        <v>1.40929388999939</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.048494338989258</v>
+        <v>1.067318201065063</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.40929388999939</v>
+        <v>1.408898115158081</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.048494338989258</v>
+        <v>1.067318201065063</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.40929388999939</v>
+        <v>1.408898115158081</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.067318201065063</v>
+        <v>1.035154342651367</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.408898115158081</v>
+        <v>1.188378095626831</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.067318201065063</v>
+        <v>1.035154342651367</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.408898115158081</v>
+        <v>1.188378095626831</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.035154342651367</v>
+        <v>74.2997670173645</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.188378095626831</v>
+        <v>85.74520540237427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.035154342651367</v>
+        <v>74.2997670173645</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.188378095626831</v>
+        <v>85.74520540237427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>74.2997670173645</v>
+        <v>7.275536298751831</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.3702735160827576</v>
       </c>
       <c r="F2" t="n">
-        <v>0.939873417721519</v>
+        <v>0.640625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9169917656074629</v>
+        <v>0.311677179496357</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9807870872172846</v>
+        <v>0.9319726562499999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>85.74520540237427</v>
+        <v>8.832409143447876</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9193219807675821</v>
+        <v>0.3944080487070005</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9413118527042578</v>
+        <v>0.6375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9190787698855583</v>
+        <v>0.313395838344505</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9801950104776356</v>
+        <v>0.9329199218749999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>74.2997670173645</v>
+        <v>7.275536298751831</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.3702735160827576</v>
       </c>
       <c r="F2" t="n">
-        <v>0.939873417721519</v>
+        <v>0.640625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9169917656074629</v>
+        <v>0.311677179496357</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9807870872172846</v>
+        <v>0.9319726562499999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>85.74520540237427</v>
+        <v>8.832409143447876</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9193219807675821</v>
+        <v>0.3944080487070005</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9413118527042578</v>
+        <v>0.6375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9190787698855583</v>
+        <v>0.313395838344505</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9801950104776356</v>
+        <v>0.9329199218749999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.275536298751831</v>
+        <v>55.87844181060791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3702735160827576</v>
+        <v>0.7663753818038094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.640625</v>
+        <v>0.9467950342031923</v>
       </c>
       <c r="G2" t="n">
-        <v>0.311677179496357</v>
+        <v>0.8046094877089758</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9319726562499999</v>
+        <v>0.9339814925136026</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.832409143447876</v>
+        <v>80.65231132507324</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3944080487070005</v>
+        <v>0.7834056300532612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6375</v>
+        <v>0.9447681783633139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.313395838344505</v>
+        <v>0.7965198332895054</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9329199218749999</v>
+        <v>0.9337574963263038</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.275536298751831</v>
+        <v>55.87844181060791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3702735160827576</v>
+        <v>0.7663753818038094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.640625</v>
+        <v>0.9467950342031923</v>
       </c>
       <c r="G2" t="n">
-        <v>0.311677179496357</v>
+        <v>0.8046094877089758</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9319726562499999</v>
+        <v>0.9339814925136026</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.832409143447876</v>
+        <v>80.65231132507324</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3944080487070005</v>
+        <v>0.7834056300532612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6375</v>
+        <v>0.9447681783633139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.313395838344505</v>
+        <v>0.7965198332895054</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9329199218749999</v>
+        <v>0.9337574963263038</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>55.87844181060791</v>
+        <v>0.9087929725646973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>80.65231132507324</v>
+        <v>1.191066265106201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9337574963263038</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>55.87844181060791</v>
+        <v>0.9087929725646973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>80.65231132507324</v>
+        <v>1.191066265106201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9337574963263038</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9087929725646973</v>
+        <v>0.8377194404602051</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.191066265106201</v>
+        <v>1.073031425476074</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9087929725646973</v>
+        <v>0.8377194404602051</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.191066265106201</v>
+        <v>1.073031425476074</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8377194404602051</v>
+        <v>0.7824199199676514</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.073031425476074</v>
+        <v>1.052121877670288</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8377194404602051</v>
+        <v>0.7824199199676514</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.073031425476074</v>
+        <v>1.052121877670288</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7824199199676514</v>
+        <v>1.180825710296631</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.052121877670288</v>
+        <v>1.669695138931274</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -543,6 +543,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.459268569946289</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967368878519636</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7824199199676514</v>
+        <v>1.180825710296631</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.052121877670288</v>
+        <v>1.669695138931274</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -674,6 +709,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.459268569946289</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967368878519636</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.180825710296631</v>
+        <v>1.073341608047485</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.669695138931274</v>
+        <v>1.492615699768066</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.459268569946289</v>
+        <v>1.971936702728271</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967368878519636</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.180825710296631</v>
+        <v>1.073341608047485</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.669695138931274</v>
+        <v>1.492615699768066</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.459268569946289</v>
+        <v>1.971936702728271</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967368878519636</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.073341608047485</v>
+        <v>42.96212124824524</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.492615699768066</v>
+        <v>56.19120001792908</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.971936702728271</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967368878519636</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9998310810810811</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.073341608047485</v>
+        <v>42.96212124824524</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.492615699768066</v>
+        <v>56.19120001792908</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.971936702728271</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967368878519636</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9998310810810811</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>42.96212124824524</v>
+        <v>333.764634847641</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9131605579577853</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.939873417721519</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9169917656074629</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9807870872172846</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>56.19120001792908</v>
+        <v>532.8627712726593</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9193219807675821</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9413118527042578</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9190787698855583</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9801950104776356</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>42.96212124824524</v>
+        <v>333.764634847641</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9131605579577853</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.939873417721519</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9169917656074629</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9807870872172846</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>56.19120001792908</v>
+        <v>532.8627712726593</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9193219807675821</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9413118527042578</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9190787698855583</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9801950104776356</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>333.764634847641</v>
+        <v>275.1872861385345</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>532.8627712726593</v>
+        <v>328.0026791095734</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>333.764634847641</v>
+        <v>275.1872861385345</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>532.8627712726593</v>
+        <v>328.0026791095734</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>275.1872861385345</v>
+        <v>58.71340918540955</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7663753818038094</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9467950342031923</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.8046094877089758</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9339814925136026</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>328.0026791095734</v>
+        <v>85.50505352020264</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7834056300532612</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9447681783633139</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7965198332895054</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9337503475118155</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>275.1872861385345</v>
+        <v>58.71340918540955</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7663753818038094</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9467950342031923</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.8046094877089758</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9339814925136026</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>328.0026791095734</v>
+        <v>85.50505352020264</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7834056300532612</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9447681783633139</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7965198332895054</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9337503475118155</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>58.71340918540955</v>
+        <v>101.9579718112946</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9414777373848328</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9529743710322126</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9445826512034934</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9902825801679586</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>85.50505352020264</v>
+        <v>208.2088785171509</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9443251101310539</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9539148836115683</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.945737748115375</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9337503475118155</v>
+        <v>0.9901785648619486</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>58.71340918540955</v>
+        <v>101.9579718112946</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9414777373848328</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9529743710322126</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9445826512034934</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9902825801679586</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>85.50505352020264</v>
+        <v>208.2088785171509</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9443251101310539</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9539148836115683</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.945737748115375</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9337503475118155</v>
+        <v>0.9901785648619486</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>101.9579718112946</v>
+        <v>10.09751319885254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9414777373848328</v>
+        <v>0.3856052350539436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9529743710322126</v>
+        <v>0.686734693877551</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9445826512034934</v>
+        <v>0.5042296191044431</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9902825801679586</v>
+        <v>0.9515792031098153</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>208.2088785171509</v>
+        <v>13.40703725814819</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9443251101310539</v>
+        <v>0.408905626066224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9539148836115683</v>
+        <v>0.6908163265306122</v>
       </c>
       <c r="G3" t="n">
-        <v>0.945737748115375</v>
+        <v>0.4947434728497458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9901785648619486</v>
+        <v>0.950504130223518</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>101.9579718112946</v>
+        <v>10.09751319885254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9414777373848328</v>
+        <v>0.3856052350539436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9529743710322126</v>
+        <v>0.686734693877551</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9445826512034934</v>
+        <v>0.5042296191044431</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9902825801679586</v>
+        <v>0.9515792031098153</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>208.2088785171509</v>
+        <v>13.40703725814819</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9443251101310539</v>
+        <v>0.408905626066224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9539148836115683</v>
+        <v>0.6908163265306122</v>
       </c>
       <c r="G3" t="n">
-        <v>0.945737748115375</v>
+        <v>0.4947434728497458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9901785648619486</v>
+        <v>0.950504130223518</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.09751319885254</v>
+        <v>1.117694854736328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3856052350539436</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.686734693877551</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5042296191044431</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9515792031098153</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -526,21 +526,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.40703725814819</v>
+        <v>1.38228440284729</v>
       </c>
       <c r="E3" t="n">
-        <v>0.408905626066224</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6908163265306122</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4947434728497458</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.950504130223518</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.826208114624023</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967368878519636</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.09751319885254</v>
+        <v>1.117694854736328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3856052350539436</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.686734693877551</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5042296191044431</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9515792031098153</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -657,21 +692,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.40703725814819</v>
+        <v>1.38228440284729</v>
       </c>
       <c r="E3" t="n">
-        <v>0.408905626066224</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6908163265306122</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4947434728497458</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.950504130223518</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.826208114624023</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967368878519636</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.117694854736328</v>
+        <v>1.220383882522583</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.38228440284729</v>
+        <v>1.690788269042969</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.826208114624023</v>
+        <v>2.594851732254028</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967368878519636</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.117694854736328</v>
+        <v>1.220383882522583</v>
       </c>
       <c r="E2" t="n">
         <v>0.9950995611895129</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.38228440284729</v>
+        <v>1.690788269042969</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.826208114624023</v>
+        <v>2.594851732254028</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967368878519636</v>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1.220383882522583</v>
+        <v>186.2187540531158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9033234438824053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9172297297297297</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9089010530018247</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9752632599844824</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.690788269042969</v>
+        <v>169.5387573242188</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9060012070323756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9172297297297297</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9089010530018247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9752632599844824</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.594851732254028</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967368878519636</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9998310810810811</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1.220383882522583</v>
+        <v>186.2187540531158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9033234438824053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9172297297297297</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9089010530018247</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9752632599844824</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.690788269042969</v>
+        <v>169.5387573242188</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9060012070323756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9172297297297297</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9089010530018247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9752632599844824</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.594851732254028</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967368878519636</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9998310810810811</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>186.2187540531158</v>
+        <v>482.6259047985077</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9033234438824053</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9172297297297297</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9089010530018247</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9752632599844824</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>169.5387573242188</v>
+        <v>373.8616678714752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9060012070323756</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9172297297297297</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9089010530018247</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9752632599844824</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>186.2187540531158</v>
+        <v>482.6259047985077</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9033234438824053</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9172297297297297</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9089010530018247</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9752632599844824</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>169.5387573242188</v>
+        <v>373.8616678714752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9060012070323756</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9172297297297297</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9089010530018247</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9752632599844824</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>482.6259047985077</v>
+        <v>248.3944759368896</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>373.8616678714752</v>
+        <v>461.5363669395447</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>482.6259047985077</v>
+        <v>248.3944759368896</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>373.8616678714752</v>
+        <v>461.5363669395447</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
